--- a/data/trans_orig/IP07A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A01-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>65980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60544</t>
+          <t>60023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79255</t>
+          <t>79859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112841</t>
+          <t>113491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139005</t>
+          <t>139974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68091</t>
+          <t>67853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71304</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109001</t>
+          <t>109506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135045</t>
+          <t>135388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>93576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115737</t>
+          <t>115849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95872</t>
+          <t>95693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118245</t>
+          <t>118751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196876</t>
+          <t>195348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228150</t>
+          <t>228255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63722</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86028</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73424</t>
+          <t>73197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96249</t>
+          <t>95846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142606</t>
+          <t>143210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175263</t>
+          <t>174650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146270</t>
+          <t>146117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175392</t>
+          <t>175764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161972</t>
+          <t>162715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>193038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>317820</t>
+          <t>318110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>358970</t>
+          <t>359192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119226</t>
+          <t>119865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149360</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161865</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262176</t>
+          <t>259218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302540</t>
+          <t>299347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70867</t>
+          <t>70981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72419</t>
+          <t>71825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>108968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137104</t>
+          <t>138180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>73009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94197</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73003</t>
+          <t>73645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94686</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153608</t>
+          <t>152125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183683</t>
+          <t>181418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60877</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61123</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81365</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108807</t>
+          <t>107112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136924</t>
+          <t>136295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93299</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114346</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>75612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96977</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174637</t>
+          <t>174820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204314</t>
+          <t>205580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97688</t>
+          <t>96566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125616</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120006</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>148468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226121</t>
+          <t>225150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265388</t>
+          <t>267728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173214</t>
+          <t>172786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201300</t>
+          <t>202834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155182</t>
+          <t>153086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184438</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337710</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378456</t>
+          <t>379046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4860,47 +4860,47 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>91242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114041</t>
+          <t>113871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100262</t>
+          <t>101048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123669</t>
+          <t>123784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199286</t>
+          <t>198221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230565</t>
+          <t>231714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60665</t>
+          <t>59874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82552</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51182</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72694</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118433</t>
+          <t>116887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148136</t>
+          <t>149172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91503</t>
+          <t>90877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88669</t>
+          <t>87688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109505</t>
+          <t>110834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164753</t>
+          <t>163723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196556</t>
+          <t>195407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66546</t>
+          <t>66416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88600</t>
+          <t>88132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>54848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>77405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128234</t>
+          <t>128553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158935</t>
+          <t>158592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167663</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197762</t>
+          <t>196516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196248</t>
+          <t>195992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>226769</t>
+          <t>227053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373805</t>
+          <t>373283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416407</t>
+          <t>415747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134047</t>
+          <t>134553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165301</t>
+          <t>164623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112117</t>
+          <t>111323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142802</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>253596</t>
+          <t>254053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297037</t>
+          <t>298391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>65973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85932</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>102507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125400</t>
+          <t>126012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174650</t>
+          <t>175426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206377</t>
+          <t>205670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38603</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>75855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104770</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139142</t>
+          <t>140415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184311</t>
+          <t>182780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145683</t>
+          <t>145985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184397</t>
+          <t>183879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295445</t>
+          <t>298550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355182</t>
+          <t>359630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89056</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>64803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>99787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126958</t>
+          <t>123242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178497</t>
+          <t>178751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214613</t>
+          <t>213956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>264072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>258431</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>299842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>481176</t>
+          <t>484370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548243</t>
+          <t>550631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91522</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138487</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104928</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212721</t>
+          <t>209710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273963</t>
+          <t>271121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
